--- a/DateBase/orders/Nha Thu_2026-9-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-4.xlsx
@@ -686,6 +686,9 @@
       <c r="C31" t="str">
         <v>780_贝壳草_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -744,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08101010710155311101621010128101035151015105510100</v>
+        <v>081010107101553111016210101281010351510151055101010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -687,12 +687,20 @@
         <v>780_贝壳草_undefined_undefined_1bunch</v>
       </c>
       <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>319_尤加利叶带果_Eucalyptus leaves with small pods_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -747,7 +755,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>081010107101553111016210101281010351510151055101010</v>
+        <v>0810101071015531110162101012810103515101510551010510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-9-4.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-4.xlsx
@@ -757,6 +757,9 @@
       <c r="G2" t="str">
         <v>0810101071015531110162101012810103515101510551010510</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
